--- a/reports/latest/Passed_Test_Cases.xlsx
+++ b/reports/latest/Passed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2491" uniqueCount="1024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="1030">
   <si>
     <t>Test ID</t>
   </si>
@@ -76,6 +76,12 @@
     <t>Authentication Verification - Case 5</t>
   </si>
   <si>
+    <t>TC_AUTH_006</t>
+  </si>
+  <si>
+    <t>Authentication Verification - Case 6</t>
+  </si>
+  <si>
     <t>TC_AUTH_007</t>
   </si>
   <si>
@@ -190,6 +196,12 @@
     <t>Authentication Verification - Case 25</t>
   </si>
   <si>
+    <t>TC_AUTH_026</t>
+  </si>
+  <si>
+    <t>Authentication Verification - Case 26</t>
+  </si>
+  <si>
     <t>TC_AUTH_027</t>
   </si>
   <si>
@@ -649,6 +661,12 @@
     <t>Profile Management Verification - Case 11</t>
   </si>
   <si>
+    <t>TC_PROF_012</t>
+  </si>
+  <si>
+    <t>Profile Management Verification - Case 12</t>
+  </si>
+  <si>
     <t>TC_PROF_013</t>
   </si>
   <si>
@@ -685,12 +703,6 @@
     <t>Profile Management Verification - Case 18</t>
   </si>
   <si>
-    <t>TC_PROF_019</t>
-  </si>
-  <si>
-    <t>Profile Management Verification - Case 19</t>
-  </si>
-  <si>
     <t>TC_PROF_020</t>
   </si>
   <si>
@@ -718,6 +730,12 @@
     <t>Navigation Verification - Case 3</t>
   </si>
   <si>
+    <t>TC_NAV_004</t>
+  </si>
+  <si>
+    <t>Navigation Verification - Case 4</t>
+  </si>
+  <si>
     <t>TC_NAV_005</t>
   </si>
   <si>
@@ -862,12 +880,6 @@
     <t>Navigation Verification - Case 28</t>
   </si>
   <si>
-    <t>TC_NAV_029</t>
-  </si>
-  <si>
-    <t>Navigation Verification - Case 29</t>
-  </si>
-  <si>
     <t>TC_NAV_030</t>
   </si>
   <si>
@@ -1090,12 +1102,6 @@
     <t>Forms Verification - Case 15</t>
   </si>
   <si>
-    <t>TC_FORM_016</t>
-  </si>
-  <si>
-    <t>Forms Verification - Case 16</t>
-  </si>
-  <si>
     <t>TC_FORM_017</t>
   </si>
   <si>
@@ -1255,12 +1261,6 @@
     <t>CRUD Operations Verification - Case 2</t>
   </si>
   <si>
-    <t>TC_CRUD_003</t>
-  </si>
-  <si>
-    <t>CRUD Operations Verification - Case 3</t>
-  </si>
-  <si>
     <t>TC_CRUD_004</t>
   </si>
   <si>
@@ -1351,12 +1351,6 @@
     <t>CRUD Operations Verification - Case 18</t>
   </si>
   <si>
-    <t>TC_CRUD_019</t>
-  </si>
-  <si>
-    <t>CRUD Operations Verification - Case 19</t>
-  </si>
-  <si>
     <t>TC_CRUD_020</t>
   </si>
   <si>
@@ -1405,6 +1399,12 @@
     <t>CRUD Operations Verification - Case 27</t>
   </si>
   <si>
+    <t>TC_CRUD_028</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 28</t>
+  </si>
+  <si>
     <t>TC_CRUD_029</t>
   </si>
   <si>
@@ -1522,10 +1522,10 @@
     <t>Search Verification - Case 7</t>
   </si>
   <si>
-    <t>TC_SRCH_009</t>
-  </si>
-  <si>
-    <t>Search Verification - Case 9</t>
+    <t>TC_SRCH_008</t>
+  </si>
+  <si>
+    <t>Search Verification - Case 8</t>
   </si>
   <si>
     <t>TC_SRCH_010</t>
@@ -1645,18 +1645,6 @@
     <t>Filters Verification - Case 8</t>
   </si>
   <si>
-    <t>TC_FILT_009</t>
-  </si>
-  <si>
-    <t>Filters Verification - Case 9</t>
-  </si>
-  <si>
-    <t>TC_FILT_010</t>
-  </si>
-  <si>
-    <t>Filters Verification - Case 10</t>
-  </si>
-  <si>
     <t>TC_FILT_011</t>
   </si>
   <si>
@@ -1705,6 +1693,12 @@
     <t>Filters Verification - Case 18</t>
   </si>
   <si>
+    <t>TC_FILT_019</t>
+  </si>
+  <si>
+    <t>Filters Verification - Case 19</t>
+  </si>
+  <si>
     <t>TC_FILT_020</t>
   </si>
   <si>
@@ -1942,6 +1936,12 @@
     <t>Input Validation Verification - Case 38</t>
   </si>
   <si>
+    <t>TC_VAL_039</t>
+  </si>
+  <si>
+    <t>Input Validation Verification - Case 39</t>
+  </si>
+  <si>
     <t>TC_VAL_040</t>
   </si>
   <si>
@@ -2560,6 +2560,12 @@
     <t>Accessibility Verification - Case 9</t>
   </si>
   <si>
+    <t>TC_ACC_010</t>
+  </si>
+  <si>
+    <t>Accessibility Verification - Case 10</t>
+  </si>
+  <si>
     <t>TC_ACC_011</t>
   </si>
   <si>
@@ -2578,12 +2584,6 @@
     <t>Accessibility Verification - Case 13</t>
   </si>
   <si>
-    <t>TC_ACC_014</t>
-  </si>
-  <si>
-    <t>Accessibility Verification - Case 14</t>
-  </si>
-  <si>
     <t>TC_ACC_015</t>
   </si>
   <si>
@@ -2620,18 +2620,12 @@
     <t>Accessibility Verification - Case 20</t>
   </si>
   <si>
-    <t>TC_RESP_001</t>
+    <t>TC_RESP_002</t>
   </si>
   <si>
     <t>Responsive UI</t>
   </si>
   <si>
-    <t>Responsive UI Verification - Case 1</t>
-  </si>
-  <si>
-    <t>TC_RESP_002</t>
-  </si>
-  <si>
     <t>Responsive UI Verification - Case 2</t>
   </si>
   <si>
@@ -2776,6 +2770,12 @@
     <t>Performance Smoke Tests Verification - Case 15</t>
   </si>
   <si>
+    <t>TC_PERF_016</t>
+  </si>
+  <si>
+    <t>Performance Smoke Tests Verification - Case 16</t>
+  </si>
+  <si>
     <t>TC_PERF_017</t>
   </si>
   <si>
@@ -2905,12 +2905,24 @@
     <t>Regression Suite Verification - Case 17</t>
   </si>
   <si>
+    <t>TC_REGR_018</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 18</t>
+  </si>
+  <si>
     <t>TC_REGR_019</t>
   </si>
   <si>
     <t>Regression Suite Verification - Case 19</t>
   </si>
   <si>
+    <t>TC_REGR_020</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 20</t>
+  </si>
+  <si>
     <t>TC_REGR_021</t>
   </si>
   <si>
@@ -3071,6 +3083,12 @@
   </si>
   <si>
     <t>Regression Suite Verification - Case 47</t>
+  </si>
+  <si>
+    <t>TC_REGR_048</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 48</t>
   </si>
   <si>
     <t>TC_REGR_049</t>
@@ -3473,7 +3491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F498"/>
+  <dimension ref="A1:F501"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3520,7 +3538,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>197</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3540,7 +3558,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3560,7 +3578,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>295</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3580,7 +3598,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>291</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3600,7 +3618,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>153</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3614,13 +3632,13 @@
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>179</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3634,13 +3652,13 @@
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3654,13 +3672,13 @@
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>217</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3674,13 +3692,13 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10">
-        <v>137</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3694,13 +3712,13 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>299</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3714,13 +3732,13 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3734,13 +3752,13 @@
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13">
-        <v>123</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3754,13 +3772,13 @@
         <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14">
-        <v>154</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3774,13 +3792,13 @@
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15">
-        <v>224</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3794,13 +3812,13 @@
         <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16">
-        <v>165</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3814,13 +3832,13 @@
         <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17">
-        <v>199</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3834,13 +3852,13 @@
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3854,13 +3872,13 @@
         <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3874,13 +3892,13 @@
         <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
       <c r="F20">
-        <v>276</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3894,13 +3912,13 @@
         <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21">
-        <v>216</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3914,13 +3932,13 @@
         <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22">
-        <v>185</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3934,13 +3952,13 @@
         <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23">
-        <v>244</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3954,13 +3972,13 @@
         <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3974,13 +3992,13 @@
         <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25">
-        <v>290</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3994,13 +4012,13 @@
         <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
       </c>
       <c r="F26">
-        <v>198</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4014,13 +4032,13 @@
         <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27">
-        <v>185</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4034,13 +4052,13 @@
         <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28">
-        <v>131</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4054,13 +4072,13 @@
         <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29">
-        <v>232</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -4074,13 +4092,13 @@
         <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30">
-        <v>187</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4094,13 +4112,13 @@
         <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
       </c>
       <c r="F31">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -4114,13 +4132,13 @@
         <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32">
-        <v>151</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -4134,13 +4152,13 @@
         <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33">
-        <v>183</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4154,13 +4172,13 @@
         <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
       </c>
       <c r="F34">
-        <v>227</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4174,13 +4192,13 @@
         <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35">
-        <v>295</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4194,13 +4212,13 @@
         <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36">
-        <v>279</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4214,13 +4232,13 @@
         <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37">
-        <v>167</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4234,13 +4252,13 @@
         <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
       </c>
       <c r="F38">
-        <v>158</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -4254,13 +4272,13 @@
         <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
       </c>
       <c r="F39">
-        <v>240</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4268,59 +4286,59 @@
         <v>87</v>
       </c>
       <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
         <v>88</v>
       </c>
-      <c r="C40" t="s">
-        <v>89</v>
-      </c>
       <c r="D40" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
       </c>
       <c r="F40">
-        <v>265</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
         <v>90</v>
       </c>
-      <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s">
-        <v>91</v>
-      </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
       </c>
       <c r="F41">
-        <v>216</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
         <v>92</v>
-      </c>
-      <c r="B42" t="s">
-        <v>88</v>
       </c>
       <c r="C42" t="s">
         <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42">
-        <v>169</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -4328,19 +4346,19 @@
         <v>94</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
         <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
       </c>
       <c r="F43">
-        <v>259</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -4348,19 +4366,19 @@
         <v>96</v>
       </c>
       <c r="B44" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
         <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -4368,19 +4386,19 @@
         <v>98</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
         <v>99</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
       </c>
       <c r="F45">
-        <v>257</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -4388,19 +4406,19 @@
         <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
         <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
       </c>
       <c r="F46">
-        <v>203</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -4408,19 +4426,19 @@
         <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
         <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
       </c>
       <c r="F47">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -4428,19 +4446,19 @@
         <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
         <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
       </c>
       <c r="F48">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4448,19 +4466,19 @@
         <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C49" t="s">
         <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
       </c>
       <c r="F49">
-        <v>224</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4468,19 +4486,19 @@
         <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C50" t="s">
         <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
       </c>
       <c r="F50">
-        <v>279</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4488,19 +4506,19 @@
         <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C51" t="s">
         <v>111</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4508,19 +4526,19 @@
         <v>112</v>
       </c>
       <c r="B52" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C52" t="s">
         <v>113</v>
       </c>
       <c r="D52" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52">
-        <v>297</v>
+        <v>281</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4528,19 +4546,19 @@
         <v>114</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C53" t="s">
         <v>115</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
       </c>
       <c r="F53">
-        <v>289</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4548,19 +4566,19 @@
         <v>116</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
         <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
       </c>
       <c r="F54">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4568,19 +4586,19 @@
         <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
         <v>119</v>
       </c>
       <c r="D55" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
       </c>
       <c r="F55">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4588,19 +4606,19 @@
         <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C56" t="s">
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
       </c>
       <c r="F56">
-        <v>264</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4608,19 +4626,19 @@
         <v>122</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C57" t="s">
         <v>123</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
       </c>
       <c r="F57">
-        <v>294</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4628,19 +4646,19 @@
         <v>124</v>
       </c>
       <c r="B58" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C58" t="s">
         <v>125</v>
       </c>
       <c r="D58" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
       </c>
       <c r="F58">
-        <v>118</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -4648,19 +4666,19 @@
         <v>126</v>
       </c>
       <c r="B59" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C59" t="s">
         <v>127</v>
       </c>
       <c r="D59" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
       </c>
       <c r="F59">
-        <v>274</v>
+        <v>138</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -4668,19 +4686,19 @@
         <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C60" t="s">
         <v>129</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
       </c>
       <c r="F60">
-        <v>217</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -4688,19 +4706,19 @@
         <v>130</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C61" t="s">
         <v>131</v>
       </c>
       <c r="D61" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
       </c>
       <c r="F61">
-        <v>257</v>
+        <v>225</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4708,19 +4726,19 @@
         <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C62" t="s">
         <v>133</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
       </c>
       <c r="F62">
-        <v>240</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -4728,19 +4746,19 @@
         <v>134</v>
       </c>
       <c r="B63" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s">
         <v>135</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
       </c>
       <c r="F63">
-        <v>251</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -4748,19 +4766,19 @@
         <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
         <v>137</v>
       </c>
       <c r="D64" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
       </c>
       <c r="F64">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4768,19 +4786,19 @@
         <v>138</v>
       </c>
       <c r="B65" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C65" t="s">
         <v>139</v>
       </c>
       <c r="D65" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
       </c>
       <c r="F65">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4788,19 +4806,19 @@
         <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C66" t="s">
         <v>141</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
       </c>
       <c r="F66">
-        <v>115</v>
+        <v>195</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4808,19 +4826,19 @@
         <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C67" t="s">
         <v>143</v>
       </c>
       <c r="D67" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
       </c>
       <c r="F67">
-        <v>122</v>
+        <v>264</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4828,19 +4846,19 @@
         <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C68" t="s">
         <v>145</v>
       </c>
       <c r="D68" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
       </c>
       <c r="F68">
-        <v>119</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -4848,19 +4866,19 @@
         <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C69" t="s">
         <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
       </c>
       <c r="F69">
-        <v>265</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4868,59 +4886,59 @@
         <v>148</v>
       </c>
       <c r="B70" t="s">
+        <v>92</v>
+      </c>
+      <c r="C70" t="s">
         <v>149</v>
       </c>
-      <c r="C70" t="s">
-        <v>150</v>
-      </c>
       <c r="D70" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
       </c>
       <c r="F70">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>150</v>
+      </c>
+      <c r="B71" t="s">
+        <v>92</v>
+      </c>
+      <c r="C71" t="s">
         <v>151</v>
       </c>
-      <c r="B71" t="s">
-        <v>149</v>
-      </c>
-      <c r="C71" t="s">
-        <v>152</v>
-      </c>
       <c r="D71" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
       </c>
       <c r="F71">
-        <v>113</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>152</v>
+      </c>
+      <c r="B72" t="s">
         <v>153</v>
-      </c>
-      <c r="B72" t="s">
-        <v>149</v>
       </c>
       <c r="C72" t="s">
         <v>154</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
       </c>
       <c r="F72">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4928,19 +4946,19 @@
         <v>155</v>
       </c>
       <c r="B73" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
         <v>156</v>
       </c>
       <c r="D73" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
       </c>
       <c r="F73">
-        <v>123</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -4948,19 +4966,19 @@
         <v>157</v>
       </c>
       <c r="B74" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C74" t="s">
         <v>158</v>
       </c>
       <c r="D74" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74">
-        <v>274</v>
+        <v>289</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4968,19 +4986,19 @@
         <v>159</v>
       </c>
       <c r="B75" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C75" t="s">
         <v>160</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
       </c>
       <c r="F75">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4988,19 +5006,19 @@
         <v>161</v>
       </c>
       <c r="B76" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C76" t="s">
         <v>162</v>
       </c>
       <c r="D76" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E76" t="s">
         <v>10</v>
       </c>
       <c r="F76">
-        <v>168</v>
+        <v>243</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5008,19 +5026,19 @@
         <v>163</v>
       </c>
       <c r="B77" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s">
         <v>164</v>
       </c>
       <c r="D77" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
       </c>
       <c r="F77">
-        <v>116</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -5028,19 +5046,19 @@
         <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C78" t="s">
         <v>166</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
       </c>
       <c r="F78">
-        <v>184</v>
+        <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -5048,19 +5066,19 @@
         <v>167</v>
       </c>
       <c r="B79" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C79" t="s">
         <v>168</v>
       </c>
       <c r="D79" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
       </c>
       <c r="F79">
-        <v>280</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -5068,19 +5086,19 @@
         <v>169</v>
       </c>
       <c r="B80" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C80" t="s">
         <v>170</v>
       </c>
       <c r="D80" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
       </c>
       <c r="F80">
-        <v>280</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -5088,19 +5106,19 @@
         <v>171</v>
       </c>
       <c r="B81" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C81" t="s">
         <v>172</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
       </c>
       <c r="F81">
-        <v>279</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -5108,19 +5126,19 @@
         <v>173</v>
       </c>
       <c r="B82" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C82" t="s">
         <v>174</v>
       </c>
       <c r="D82" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
       </c>
       <c r="F82">
-        <v>109</v>
+        <v>279</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -5128,19 +5146,19 @@
         <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C83" t="s">
         <v>176</v>
       </c>
       <c r="D83" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
       </c>
       <c r="F83">
-        <v>285</v>
+        <v>253</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5148,19 +5166,19 @@
         <v>177</v>
       </c>
       <c r="B84" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C84" t="s">
         <v>178</v>
       </c>
       <c r="D84" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E84" t="s">
         <v>10</v>
       </c>
       <c r="F84">
-        <v>281</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -5168,19 +5186,19 @@
         <v>179</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C85" t="s">
         <v>180</v>
       </c>
       <c r="D85" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
       </c>
       <c r="F85">
-        <v>109</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -5188,19 +5206,19 @@
         <v>181</v>
       </c>
       <c r="B86" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C86" t="s">
         <v>182</v>
       </c>
       <c r="D86" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
       </c>
       <c r="F86">
-        <v>244</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -5208,19 +5226,19 @@
         <v>183</v>
       </c>
       <c r="B87" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C87" t="s">
         <v>184</v>
       </c>
       <c r="D87" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
       </c>
       <c r="F87">
-        <v>272</v>
+        <v>294</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -5228,19 +5246,19 @@
         <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C88" t="s">
         <v>186</v>
       </c>
       <c r="D88" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
       </c>
       <c r="F88">
-        <v>192</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -5248,19 +5266,19 @@
         <v>187</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C89" t="s">
         <v>188</v>
       </c>
       <c r="D89" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
       </c>
       <c r="F89">
-        <v>205</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -5268,11 +5286,11 @@
         <v>189</v>
       </c>
       <c r="B90" t="s">
+        <v>153</v>
+      </c>
+      <c r="C90" t="s">
         <v>190</v>
       </c>
-      <c r="C90" t="s">
-        <v>191</v>
-      </c>
       <c r="D90" t="s">
         <v>9</v>
       </c>
@@ -5280,19 +5298,19 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>260</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>191</v>
+      </c>
+      <c r="B91" t="s">
+        <v>153</v>
+      </c>
+      <c r="C91" t="s">
         <v>192</v>
       </c>
-      <c r="B91" t="s">
-        <v>190</v>
-      </c>
-      <c r="C91" t="s">
-        <v>193</v>
-      </c>
       <c r="D91" t="s">
         <v>13</v>
       </c>
@@ -5300,27 +5318,27 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>178</v>
+        <v>264</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>193</v>
+      </c>
+      <c r="B92" t="s">
         <v>194</v>
-      </c>
-      <c r="B92" t="s">
-        <v>190</v>
       </c>
       <c r="C92" t="s">
         <v>195</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
       </c>
       <c r="F92">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -5328,19 +5346,19 @@
         <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C93" t="s">
         <v>197</v>
       </c>
       <c r="D93" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E93" t="s">
         <v>10</v>
       </c>
       <c r="F93">
-        <v>219</v>
+        <v>256</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -5348,19 +5366,19 @@
         <v>198</v>
       </c>
       <c r="B94" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C94" t="s">
         <v>199</v>
       </c>
       <c r="D94" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E94" t="s">
         <v>10</v>
       </c>
       <c r="F94">
-        <v>182</v>
+        <v>278</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -5368,19 +5386,19 @@
         <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C95" t="s">
         <v>201</v>
       </c>
       <c r="D95" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E95" t="s">
         <v>10</v>
       </c>
       <c r="F95">
-        <v>242</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -5388,19 +5406,19 @@
         <v>202</v>
       </c>
       <c r="B96" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C96" t="s">
         <v>203</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
       </c>
       <c r="F96">
-        <v>207</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -5408,19 +5426,19 @@
         <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C97" t="s">
         <v>205</v>
       </c>
       <c r="D97" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
       </c>
       <c r="F97">
-        <v>228</v>
+        <v>130</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -5428,19 +5446,19 @@
         <v>206</v>
       </c>
       <c r="B98" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C98" t="s">
         <v>207</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
       </c>
       <c r="F98">
-        <v>268</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -5448,19 +5466,19 @@
         <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C99" t="s">
         <v>209</v>
       </c>
       <c r="D99" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
       </c>
       <c r="F99">
-        <v>252</v>
+        <v>283</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -5468,19 +5486,19 @@
         <v>210</v>
       </c>
       <c r="B100" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C100" t="s">
         <v>211</v>
       </c>
       <c r="D100" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
       </c>
       <c r="F100">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -5488,7 +5506,7 @@
         <v>212</v>
       </c>
       <c r="B101" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C101" t="s">
         <v>213</v>
@@ -5500,7 +5518,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -5508,7 +5526,7 @@
         <v>214</v>
       </c>
       <c r="B102" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C102" t="s">
         <v>215</v>
@@ -5520,7 +5538,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>213</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -5528,7 +5546,7 @@
         <v>216</v>
       </c>
       <c r="B103" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C103" t="s">
         <v>217</v>
@@ -5540,7 +5558,7 @@
         <v>10</v>
       </c>
       <c r="F103">
-        <v>142</v>
+        <v>169</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -5548,7 +5566,7 @@
         <v>218</v>
       </c>
       <c r="B104" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C104" t="s">
         <v>219</v>
@@ -5560,7 +5578,7 @@
         <v>10</v>
       </c>
       <c r="F104">
-        <v>151</v>
+        <v>298</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -5568,7 +5586,7 @@
         <v>220</v>
       </c>
       <c r="B105" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C105" t="s">
         <v>221</v>
@@ -5580,7 +5598,7 @@
         <v>10</v>
       </c>
       <c r="F105">
-        <v>116</v>
+        <v>186</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -5588,7 +5606,7 @@
         <v>222</v>
       </c>
       <c r="B106" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C106" t="s">
         <v>223</v>
@@ -5600,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>264</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -5608,7 +5626,7 @@
         <v>224</v>
       </c>
       <c r="B107" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C107" t="s">
         <v>225</v>
@@ -5620,7 +5638,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>226</v>
+        <v>283</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -5628,7 +5646,7 @@
         <v>226</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C108" t="s">
         <v>227</v>
@@ -5640,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>293</v>
+        <v>284</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -5648,31 +5666,31 @@
         <v>228</v>
       </c>
       <c r="B109" t="s">
+        <v>194</v>
+      </c>
+      <c r="C109" t="s">
         <v>229</v>
       </c>
-      <c r="C109" t="s">
-        <v>230</v>
-      </c>
       <c r="D109" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
       </c>
       <c r="F109">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>230</v>
+      </c>
+      <c r="B110" t="s">
+        <v>194</v>
+      </c>
+      <c r="C110" t="s">
         <v>231</v>
       </c>
-      <c r="B110" t="s">
-        <v>229</v>
-      </c>
-      <c r="C110" t="s">
-        <v>232</v>
-      </c>
       <c r="D110" t="s">
         <v>13</v>
       </c>
@@ -5680,21 +5698,21 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>108</v>
+        <v>271</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>232</v>
+      </c>
+      <c r="B111" t="s">
         <v>233</v>
-      </c>
-      <c r="B111" t="s">
-        <v>229</v>
       </c>
       <c r="C111" t="s">
         <v>234</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E111" t="s">
         <v>10</v>
@@ -5708,7 +5726,7 @@
         <v>235</v>
       </c>
       <c r="B112" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C112" t="s">
         <v>236</v>
@@ -5720,7 +5738,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>160</v>
+        <v>295</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -5728,7 +5746,7 @@
         <v>237</v>
       </c>
       <c r="B113" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C113" t="s">
         <v>238</v>
@@ -5740,7 +5758,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -5748,7 +5766,7 @@
         <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C114" t="s">
         <v>240</v>
@@ -5760,7 +5778,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>281</v>
+        <v>189</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -5768,7 +5786,7 @@
         <v>241</v>
       </c>
       <c r="B115" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C115" t="s">
         <v>242</v>
@@ -5780,7 +5798,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>162</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -5788,7 +5806,7 @@
         <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C116" t="s">
         <v>244</v>
@@ -5800,7 +5818,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -5808,7 +5826,7 @@
         <v>245</v>
       </c>
       <c r="B117" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C117" t="s">
         <v>246</v>
@@ -5820,7 +5838,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>106</v>
+        <v>184</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -5828,7 +5846,7 @@
         <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C118" t="s">
         <v>248</v>
@@ -5840,7 +5858,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>169</v>
+        <v>239</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -5848,7 +5866,7 @@
         <v>249</v>
       </c>
       <c r="B119" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C119" t="s">
         <v>250</v>
@@ -5860,7 +5878,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>256</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -5868,7 +5886,7 @@
         <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C120" t="s">
         <v>252</v>
@@ -5880,7 +5898,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>173</v>
+        <v>187</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -5888,7 +5906,7 @@
         <v>253</v>
       </c>
       <c r="B121" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C121" t="s">
         <v>254</v>
@@ -5900,7 +5918,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>197</v>
+        <v>134</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -5908,7 +5926,7 @@
         <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C122" t="s">
         <v>256</v>
@@ -5920,7 +5938,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -5928,7 +5946,7 @@
         <v>257</v>
       </c>
       <c r="B123" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C123" t="s">
         <v>258</v>
@@ -5940,7 +5958,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>126</v>
+        <v>283</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -5948,7 +5966,7 @@
         <v>259</v>
       </c>
       <c r="B124" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C124" t="s">
         <v>260</v>
@@ -5960,7 +5978,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>156</v>
+        <v>206</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -5968,7 +5986,7 @@
         <v>261</v>
       </c>
       <c r="B125" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C125" t="s">
         <v>262</v>
@@ -5980,7 +5998,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>298</v>
+        <v>226</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -5988,7 +6006,7 @@
         <v>263</v>
       </c>
       <c r="B126" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C126" t="s">
         <v>264</v>
@@ -6000,7 +6018,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -6008,7 +6026,7 @@
         <v>265</v>
       </c>
       <c r="B127" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C127" t="s">
         <v>266</v>
@@ -6020,7 +6038,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>218</v>
+        <v>162</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -6028,7 +6046,7 @@
         <v>267</v>
       </c>
       <c r="B128" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C128" t="s">
         <v>268</v>
@@ -6040,7 +6058,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>244</v>
+        <v>183</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6048,7 +6066,7 @@
         <v>269</v>
       </c>
       <c r="B129" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C129" t="s">
         <v>270</v>
@@ -6060,7 +6078,7 @@
         <v>10</v>
       </c>
       <c r="F129">
-        <v>184</v>
+        <v>144</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -6068,7 +6086,7 @@
         <v>271</v>
       </c>
       <c r="B130" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C130" t="s">
         <v>272</v>
@@ -6080,7 +6098,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>218</v>
+        <v>167</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -6088,7 +6106,7 @@
         <v>273</v>
       </c>
       <c r="B131" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C131" t="s">
         <v>274</v>
@@ -6100,7 +6118,7 @@
         <v>10</v>
       </c>
       <c r="F131">
-        <v>100</v>
+        <v>206</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -6108,7 +6126,7 @@
         <v>275</v>
       </c>
       <c r="B132" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C132" t="s">
         <v>276</v>
@@ -6120,7 +6138,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>244</v>
+        <v>126</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -6128,7 +6146,7 @@
         <v>277</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C133" t="s">
         <v>278</v>
@@ -6140,7 +6158,7 @@
         <v>10</v>
       </c>
       <c r="F133">
-        <v>132</v>
+        <v>296</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -6148,7 +6166,7 @@
         <v>279</v>
       </c>
       <c r="B134" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C134" t="s">
         <v>280</v>
@@ -6160,7 +6178,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>209</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -6168,7 +6186,7 @@
         <v>281</v>
       </c>
       <c r="B135" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C135" t="s">
         <v>282</v>
@@ -6180,7 +6198,7 @@
         <v>10</v>
       </c>
       <c r="F135">
-        <v>239</v>
+        <v>267</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -6188,7 +6206,7 @@
         <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C136" t="s">
         <v>284</v>
@@ -6200,7 +6218,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -6208,7 +6226,7 @@
         <v>285</v>
       </c>
       <c r="B137" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C137" t="s">
         <v>286</v>
@@ -6220,7 +6238,7 @@
         <v>10</v>
       </c>
       <c r="F137">
-        <v>247</v>
+        <v>195</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -6228,11 +6246,11 @@
         <v>287</v>
       </c>
       <c r="B138" t="s">
+        <v>233</v>
+      </c>
+      <c r="C138" t="s">
         <v>288</v>
       </c>
-      <c r="C138" t="s">
-        <v>289</v>
-      </c>
       <c r="D138" t="s">
         <v>9</v>
       </c>
@@ -6240,47 +6258,47 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>289</v>
+      </c>
+      <c r="B139" t="s">
+        <v>233</v>
+      </c>
+      <c r="C139" t="s">
         <v>290</v>
       </c>
-      <c r="B139" t="s">
-        <v>288</v>
-      </c>
-      <c r="C139" t="s">
-        <v>291</v>
-      </c>
       <c r="D139" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
       </c>
       <c r="F139">
-        <v>299</v>
+        <v>135</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>291</v>
+      </c>
+      <c r="B140" t="s">
         <v>292</v>
-      </c>
-      <c r="B140" t="s">
-        <v>288</v>
       </c>
       <c r="C140" t="s">
         <v>293</v>
       </c>
       <c r="D140" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
       </c>
       <c r="F140">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -6288,19 +6306,19 @@
         <v>294</v>
       </c>
       <c r="B141" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C141" t="s">
         <v>295</v>
       </c>
       <c r="D141" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
       </c>
       <c r="F141">
-        <v>207</v>
+        <v>229</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -6308,13 +6326,13 @@
         <v>296</v>
       </c>
       <c r="B142" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C142" t="s">
         <v>297</v>
       </c>
       <c r="D142" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -6328,19 +6346,19 @@
         <v>298</v>
       </c>
       <c r="B143" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C143" t="s">
         <v>299</v>
       </c>
       <c r="D143" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
       </c>
       <c r="F143">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -6348,19 +6366,19 @@
         <v>300</v>
       </c>
       <c r="B144" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C144" t="s">
         <v>301</v>
       </c>
       <c r="D144" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
       </c>
       <c r="F144">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -6368,19 +6386,19 @@
         <v>302</v>
       </c>
       <c r="B145" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C145" t="s">
         <v>303</v>
       </c>
       <c r="D145" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
       </c>
       <c r="F145">
-        <v>115</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -6388,19 +6406,19 @@
         <v>304</v>
       </c>
       <c r="B146" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C146" t="s">
         <v>305</v>
       </c>
       <c r="D146" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
       </c>
       <c r="F146">
-        <v>100</v>
+        <v>141</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -6408,19 +6426,19 @@
         <v>306</v>
       </c>
       <c r="B147" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C147" t="s">
         <v>307</v>
       </c>
       <c r="D147" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
       </c>
       <c r="F147">
-        <v>253</v>
+        <v>202</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -6428,19 +6446,19 @@
         <v>308</v>
       </c>
       <c r="B148" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C148" t="s">
         <v>309</v>
       </c>
       <c r="D148" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
       </c>
       <c r="F148">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -6448,19 +6466,19 @@
         <v>310</v>
       </c>
       <c r="B149" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C149" t="s">
         <v>311</v>
       </c>
       <c r="D149" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
       </c>
       <c r="F149">
-        <v>195</v>
+        <v>298</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -6468,19 +6486,19 @@
         <v>312</v>
       </c>
       <c r="B150" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C150" t="s">
         <v>313</v>
       </c>
       <c r="D150" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
       </c>
       <c r="F150">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -6488,19 +6506,19 @@
         <v>314</v>
       </c>
       <c r="B151" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C151" t="s">
         <v>315</v>
       </c>
       <c r="D151" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
       </c>
       <c r="F151">
-        <v>230</v>
+        <v>277</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -6508,19 +6526,19 @@
         <v>316</v>
       </c>
       <c r="B152" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C152" t="s">
         <v>317</v>
       </c>
       <c r="D152" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
       </c>
       <c r="F152">
-        <v>184</v>
+        <v>152</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -6528,19 +6546,19 @@
         <v>318</v>
       </c>
       <c r="B153" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C153" t="s">
         <v>319</v>
       </c>
       <c r="D153" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E153" t="s">
         <v>10</v>
       </c>
       <c r="F153">
-        <v>157</v>
+        <v>118</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -6548,19 +6566,19 @@
         <v>320</v>
       </c>
       <c r="B154" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C154" t="s">
         <v>321</v>
       </c>
       <c r="D154" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E154" t="s">
         <v>10</v>
       </c>
       <c r="F154">
-        <v>126</v>
+        <v>267</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -6568,19 +6586,19 @@
         <v>322</v>
       </c>
       <c r="B155" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C155" t="s">
         <v>323</v>
       </c>
       <c r="D155" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E155" t="s">
         <v>10</v>
       </c>
       <c r="F155">
-        <v>154</v>
+        <v>266</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -6588,19 +6606,19 @@
         <v>324</v>
       </c>
       <c r="B156" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C156" t="s">
         <v>325</v>
       </c>
       <c r="D156" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E156" t="s">
         <v>10</v>
       </c>
       <c r="F156">
-        <v>178</v>
+        <v>239</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -6608,19 +6626,19 @@
         <v>326</v>
       </c>
       <c r="B157" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C157" t="s">
         <v>327</v>
       </c>
       <c r="D157" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
       </c>
       <c r="F157">
-        <v>295</v>
+        <v>116</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -6628,11 +6646,11 @@
         <v>328</v>
       </c>
       <c r="B158" t="s">
+        <v>292</v>
+      </c>
+      <c r="C158" t="s">
         <v>329</v>
       </c>
-      <c r="C158" t="s">
-        <v>330</v>
-      </c>
       <c r="D158" t="s">
         <v>9</v>
       </c>
@@ -6640,19 +6658,19 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>195</v>
+        <v>147</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>330</v>
+      </c>
+      <c r="B159" t="s">
+        <v>292</v>
+      </c>
+      <c r="C159" t="s">
         <v>331</v>
       </c>
-      <c r="B159" t="s">
-        <v>329</v>
-      </c>
-      <c r="C159" t="s">
-        <v>332</v>
-      </c>
       <c r="D159" t="s">
         <v>13</v>
       </c>
@@ -6660,27 +6678,27 @@
         <v>10</v>
       </c>
       <c r="F159">
-        <v>102</v>
+        <v>157</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>332</v>
+      </c>
+      <c r="B160" t="s">
         <v>333</v>
-      </c>
-      <c r="B160" t="s">
-        <v>329</v>
       </c>
       <c r="C160" t="s">
         <v>334</v>
       </c>
       <c r="D160" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E160" t="s">
         <v>10</v>
       </c>
       <c r="F160">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -6688,19 +6706,19 @@
         <v>335</v>
       </c>
       <c r="B161" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C161" t="s">
         <v>336</v>
       </c>
       <c r="D161" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
       </c>
       <c r="F161">
-        <v>148</v>
+        <v>120</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -6708,19 +6726,19 @@
         <v>337</v>
       </c>
       <c r="B162" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C162" t="s">
         <v>338</v>
       </c>
       <c r="D162" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E162" t="s">
         <v>10</v>
       </c>
       <c r="F162">
-        <v>294</v>
+        <v>195</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -6728,19 +6746,19 @@
         <v>339</v>
       </c>
       <c r="B163" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C163" t="s">
         <v>340</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
       </c>
       <c r="F163">
-        <v>132</v>
+        <v>262</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -6748,19 +6766,19 @@
         <v>341</v>
       </c>
       <c r="B164" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C164" t="s">
         <v>342</v>
       </c>
       <c r="D164" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
       </c>
       <c r="F164">
-        <v>113</v>
+        <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -6768,19 +6786,19 @@
         <v>343</v>
       </c>
       <c r="B165" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C165" t="s">
         <v>344</v>
       </c>
       <c r="D165" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E165" t="s">
         <v>10</v>
       </c>
       <c r="F165">
-        <v>180</v>
+        <v>288</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6788,19 +6806,19 @@
         <v>345</v>
       </c>
       <c r="B166" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C166" t="s">
         <v>346</v>
       </c>
       <c r="D166" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E166" t="s">
         <v>10</v>
       </c>
       <c r="F166">
-        <v>268</v>
+        <v>224</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -6808,19 +6826,19 @@
         <v>347</v>
       </c>
       <c r="B167" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C167" t="s">
         <v>348</v>
       </c>
       <c r="D167" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E167" t="s">
         <v>10</v>
       </c>
       <c r="F167">
-        <v>129</v>
+        <v>219</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -6828,19 +6846,19 @@
         <v>349</v>
       </c>
       <c r="B168" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C168" t="s">
         <v>350</v>
       </c>
       <c r="D168" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
       </c>
       <c r="F168">
-        <v>143</v>
+        <v>296</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -6848,19 +6866,19 @@
         <v>351</v>
       </c>
       <c r="B169" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C169" t="s">
         <v>352</v>
       </c>
       <c r="D169" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E169" t="s">
         <v>10</v>
       </c>
       <c r="F169">
-        <v>209</v>
+        <v>100</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -6868,19 +6886,19 @@
         <v>353</v>
       </c>
       <c r="B170" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C170" t="s">
         <v>354</v>
       </c>
       <c r="D170" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E170" t="s">
         <v>10</v>
       </c>
       <c r="F170">
-        <v>218</v>
+        <v>157</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -6888,19 +6906,19 @@
         <v>355</v>
       </c>
       <c r="B171" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C171" t="s">
         <v>356</v>
       </c>
       <c r="D171" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E171" t="s">
         <v>10</v>
       </c>
       <c r="F171">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -6908,19 +6926,19 @@
         <v>357</v>
       </c>
       <c r="B172" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C172" t="s">
         <v>358</v>
       </c>
       <c r="D172" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E172" t="s">
         <v>10</v>
       </c>
       <c r="F172">
-        <v>149</v>
+        <v>212</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -6928,19 +6946,19 @@
         <v>359</v>
       </c>
       <c r="B173" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C173" t="s">
         <v>360</v>
       </c>
       <c r="D173" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E173" t="s">
         <v>10</v>
       </c>
       <c r="F173">
-        <v>171</v>
+        <v>255</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -6948,19 +6966,19 @@
         <v>361</v>
       </c>
       <c r="B174" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C174" t="s">
         <v>362</v>
       </c>
       <c r="D174" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E174" t="s">
         <v>10</v>
       </c>
       <c r="F174">
-        <v>119</v>
+        <v>280</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6968,19 +6986,19 @@
         <v>363</v>
       </c>
       <c r="B175" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C175" t="s">
         <v>364</v>
       </c>
       <c r="D175" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E175" t="s">
         <v>10</v>
       </c>
       <c r="F175">
-        <v>216</v>
+        <v>168</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6988,19 +7006,19 @@
         <v>365</v>
       </c>
       <c r="B176" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C176" t="s">
         <v>366</v>
       </c>
       <c r="D176" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E176" t="s">
         <v>10</v>
       </c>
       <c r="F176">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -7008,19 +7026,19 @@
         <v>367</v>
       </c>
       <c r="B177" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C177" t="s">
         <v>368</v>
       </c>
       <c r="D177" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E177" t="s">
         <v>10</v>
       </c>
       <c r="F177">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -7028,19 +7046,19 @@
         <v>369</v>
       </c>
       <c r="B178" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C178" t="s">
         <v>370</v>
       </c>
       <c r="D178" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E178" t="s">
         <v>10</v>
       </c>
       <c r="F178">
-        <v>175</v>
+        <v>268</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -7048,19 +7066,19 @@
         <v>371</v>
       </c>
       <c r="B179" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C179" t="s">
         <v>372</v>
       </c>
       <c r="D179" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E179" t="s">
         <v>10</v>
       </c>
       <c r="F179">
-        <v>202</v>
+        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -7068,19 +7086,19 @@
         <v>373</v>
       </c>
       <c r="B180" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C180" t="s">
         <v>374</v>
       </c>
       <c r="D180" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E180" t="s">
         <v>10</v>
       </c>
       <c r="F180">
-        <v>166</v>
+        <v>233</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -7088,19 +7106,19 @@
         <v>375</v>
       </c>
       <c r="B181" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C181" t="s">
         <v>376</v>
       </c>
       <c r="D181" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E181" t="s">
         <v>10</v>
       </c>
       <c r="F181">
-        <v>188</v>
+        <v>154</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -7108,19 +7126,19 @@
         <v>377</v>
       </c>
       <c r="B182" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C182" t="s">
         <v>378</v>
       </c>
       <c r="D182" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E182" t="s">
         <v>10</v>
       </c>
       <c r="F182">
-        <v>189</v>
+        <v>115</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -7128,19 +7146,19 @@
         <v>379</v>
       </c>
       <c r="B183" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C183" t="s">
         <v>380</v>
       </c>
       <c r="D183" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E183" t="s">
         <v>10</v>
       </c>
       <c r="F183">
-        <v>165</v>
+        <v>206</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -7148,19 +7166,19 @@
         <v>381</v>
       </c>
       <c r="B184" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C184" t="s">
         <v>382</v>
       </c>
       <c r="D184" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E184" t="s">
         <v>10</v>
       </c>
       <c r="F184">
-        <v>122</v>
+        <v>237</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -7168,19 +7186,19 @@
         <v>383</v>
       </c>
       <c r="B185" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C185" t="s">
         <v>384</v>
       </c>
       <c r="D185" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E185" t="s">
         <v>10</v>
       </c>
       <c r="F185">
-        <v>106</v>
+        <v>191</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -7188,19 +7206,19 @@
         <v>385</v>
       </c>
       <c r="B186" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C186" t="s">
         <v>386</v>
       </c>
       <c r="D186" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E186" t="s">
         <v>10</v>
       </c>
       <c r="F186">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -7208,19 +7226,19 @@
         <v>387</v>
       </c>
       <c r="B187" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C187" t="s">
         <v>388</v>
       </c>
       <c r="D187" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E187" t="s">
         <v>10</v>
       </c>
       <c r="F187">
-        <v>226</v>
+        <v>129</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -7228,19 +7246,19 @@
         <v>389</v>
       </c>
       <c r="B188" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C188" t="s">
         <v>390</v>
       </c>
       <c r="D188" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E188" t="s">
         <v>10</v>
       </c>
       <c r="F188">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -7248,19 +7266,19 @@
         <v>391</v>
       </c>
       <c r="B189" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C189" t="s">
         <v>392</v>
       </c>
       <c r="D189" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E189" t="s">
         <v>10</v>
       </c>
       <c r="F189">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -7268,19 +7286,19 @@
         <v>393</v>
       </c>
       <c r="B190" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C190" t="s">
         <v>394</v>
       </c>
       <c r="D190" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E190" t="s">
         <v>10</v>
       </c>
       <c r="F190">
-        <v>159</v>
+        <v>130</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -7288,19 +7306,19 @@
         <v>395</v>
       </c>
       <c r="B191" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C191" t="s">
         <v>396</v>
       </c>
       <c r="D191" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E191" t="s">
         <v>10</v>
       </c>
       <c r="F191">
-        <v>111</v>
+        <v>262</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -7308,19 +7326,19 @@
         <v>397</v>
       </c>
       <c r="B192" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C192" t="s">
         <v>398</v>
       </c>
       <c r="D192" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E192" t="s">
         <v>10</v>
       </c>
       <c r="F192">
-        <v>258</v>
+        <v>142</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -7328,19 +7346,19 @@
         <v>399</v>
       </c>
       <c r="B193" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C193" t="s">
         <v>400</v>
       </c>
       <c r="D193" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E193" t="s">
         <v>10</v>
       </c>
       <c r="F193">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -7348,19 +7366,19 @@
         <v>401</v>
       </c>
       <c r="B194" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C194" t="s">
         <v>402</v>
       </c>
       <c r="D194" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E194" t="s">
         <v>10</v>
       </c>
       <c r="F194">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -7368,19 +7386,19 @@
         <v>403</v>
       </c>
       <c r="B195" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C195" t="s">
         <v>404</v>
       </c>
       <c r="D195" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E195" t="s">
         <v>10</v>
       </c>
       <c r="F195">
-        <v>195</v>
+        <v>280</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -7388,19 +7406,19 @@
         <v>405</v>
       </c>
       <c r="B196" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C196" t="s">
         <v>406</v>
       </c>
       <c r="D196" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E196" t="s">
         <v>10</v>
       </c>
       <c r="F196">
-        <v>226</v>
+        <v>190</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -7408,19 +7426,19 @@
         <v>407</v>
       </c>
       <c r="B197" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C197" t="s">
         <v>408</v>
       </c>
       <c r="D197" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E197" t="s">
         <v>10</v>
       </c>
       <c r="F197">
-        <v>272</v>
+        <v>289</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -7428,11 +7446,11 @@
         <v>409</v>
       </c>
       <c r="B198" t="s">
+        <v>333</v>
+      </c>
+      <c r="C198" t="s">
         <v>410</v>
       </c>
-      <c r="C198" t="s">
-        <v>411</v>
-      </c>
       <c r="D198" t="s">
         <v>9</v>
       </c>
@@ -7440,27 +7458,27 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>157</v>
+        <v>270</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>411</v>
+      </c>
+      <c r="B199" t="s">
         <v>412</v>
-      </c>
-      <c r="B199" t="s">
-        <v>410</v>
       </c>
       <c r="C199" t="s">
         <v>413</v>
       </c>
       <c r="D199" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E199" t="s">
         <v>10</v>
       </c>
       <c r="F199">
-        <v>287</v>
+        <v>169</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -7468,19 +7486,19 @@
         <v>414</v>
       </c>
       <c r="B200" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C200" t="s">
         <v>415</v>
       </c>
       <c r="D200" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E200" t="s">
         <v>10</v>
       </c>
       <c r="F200">
-        <v>266</v>
+        <v>154</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -7488,7 +7506,7 @@
         <v>416</v>
       </c>
       <c r="B201" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C201" t="s">
         <v>417</v>
@@ -7500,7 +7518,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>210</v>
+        <v>166</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -7508,7 +7526,7 @@
         <v>418</v>
       </c>
       <c r="B202" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C202" t="s">
         <v>419</v>
@@ -7520,7 +7538,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>211</v>
+        <v>153</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -7528,7 +7546,7 @@
         <v>420</v>
       </c>
       <c r="B203" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C203" t="s">
         <v>421</v>
@@ -7540,7 +7558,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>152</v>
+        <v>273</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -7548,7 +7566,7 @@
         <v>422</v>
       </c>
       <c r="B204" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C204" t="s">
         <v>423</v>
@@ -7560,7 +7578,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>257</v>
+        <v>100</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -7568,7 +7586,7 @@
         <v>424</v>
       </c>
       <c r="B205" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C205" t="s">
         <v>425</v>
@@ -7580,7 +7598,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>111</v>
+        <v>287</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -7588,7 +7606,7 @@
         <v>426</v>
       </c>
       <c r="B206" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C206" t="s">
         <v>427</v>
@@ -7600,7 +7618,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>223</v>
+        <v>293</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -7608,7 +7626,7 @@
         <v>428</v>
       </c>
       <c r="B207" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C207" t="s">
         <v>429</v>
@@ -7620,7 +7638,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>199</v>
+        <v>240</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -7628,7 +7646,7 @@
         <v>430</v>
       </c>
       <c r="B208" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C208" t="s">
         <v>431</v>
@@ -7640,7 +7658,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>134</v>
+        <v>274</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -7648,7 +7666,7 @@
         <v>432</v>
       </c>
       <c r="B209" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C209" t="s">
         <v>433</v>
@@ -7660,7 +7678,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>254</v>
+        <v>123</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -7668,7 +7686,7 @@
         <v>434</v>
       </c>
       <c r="B210" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C210" t="s">
         <v>435</v>
@@ -7680,7 +7698,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>157</v>
+        <v>194</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -7688,7 +7706,7 @@
         <v>436</v>
       </c>
       <c r="B211" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C211" t="s">
         <v>437</v>
@@ -7700,7 +7718,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>274</v>
+        <v>223</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -7708,7 +7726,7 @@
         <v>438</v>
       </c>
       <c r="B212" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C212" t="s">
         <v>439</v>
@@ -7720,7 +7738,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>109</v>
+        <v>189</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -7728,7 +7746,7 @@
         <v>440</v>
       </c>
       <c r="B213" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C213" t="s">
         <v>441</v>
@@ -7740,7 +7758,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>158</v>
+        <v>193</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -7748,7 +7766,7 @@
         <v>442</v>
       </c>
       <c r="B214" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C214" t="s">
         <v>443</v>
@@ -7760,7 +7778,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>234</v>
+        <v>104</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -7768,7 +7786,7 @@
         <v>444</v>
       </c>
       <c r="B215" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C215" t="s">
         <v>445</v>
@@ -7780,7 +7798,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>176</v>
+        <v>145</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7788,19 +7806,19 @@
         <v>446</v>
       </c>
       <c r="B216" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C216" t="s">
         <v>447</v>
       </c>
       <c r="D216" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E216" t="s">
         <v>10</v>
       </c>
       <c r="F216">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -7808,19 +7826,19 @@
         <v>448</v>
       </c>
       <c r="B217" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C217" t="s">
         <v>449</v>
       </c>
       <c r="D217" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E217" t="s">
         <v>10</v>
       </c>
       <c r="F217">
-        <v>249</v>
+        <v>151</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -7828,19 +7846,19 @@
         <v>450</v>
       </c>
       <c r="B218" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C218" t="s">
         <v>451</v>
       </c>
       <c r="D218" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
       </c>
       <c r="F218">
-        <v>190</v>
+        <v>248</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -7848,19 +7866,19 @@
         <v>452</v>
       </c>
       <c r="B219" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C219" t="s">
         <v>453</v>
       </c>
       <c r="D219" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E219" t="s">
         <v>10</v>
       </c>
       <c r="F219">
-        <v>183</v>
+        <v>137</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7868,19 +7886,19 @@
         <v>454</v>
       </c>
       <c r="B220" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C220" t="s">
         <v>455</v>
       </c>
       <c r="D220" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E220" t="s">
         <v>10</v>
       </c>
       <c r="F220">
-        <v>128</v>
+        <v>177</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7888,19 +7906,19 @@
         <v>456</v>
       </c>
       <c r="B221" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C221" t="s">
         <v>457</v>
       </c>
       <c r="D221" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E221" t="s">
         <v>10</v>
       </c>
       <c r="F221">
-        <v>242</v>
+        <v>290</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7908,19 +7926,19 @@
         <v>458</v>
       </c>
       <c r="B222" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C222" t="s">
         <v>459</v>
       </c>
       <c r="D222" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E222" t="s">
         <v>10</v>
       </c>
       <c r="F222">
-        <v>110</v>
+        <v>214</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7928,19 +7946,19 @@
         <v>460</v>
       </c>
       <c r="B223" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C223" t="s">
         <v>461</v>
       </c>
       <c r="D223" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E223" t="s">
         <v>10</v>
       </c>
       <c r="F223">
-        <v>182</v>
+        <v>114</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7948,19 +7966,19 @@
         <v>462</v>
       </c>
       <c r="B224" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C224" t="s">
         <v>463</v>
       </c>
       <c r="D224" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E224" t="s">
         <v>10</v>
       </c>
       <c r="F224">
-        <v>262</v>
+        <v>184</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7968,7 +7986,7 @@
         <v>464</v>
       </c>
       <c r="B225" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C225" t="s">
         <v>465</v>
@@ -7980,7 +7998,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>264</v>
+        <v>194</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7988,7 +8006,7 @@
         <v>466</v>
       </c>
       <c r="B226" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C226" t="s">
         <v>467</v>
@@ -8000,7 +8018,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>189</v>
+        <v>104</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -8008,7 +8026,7 @@
         <v>468</v>
       </c>
       <c r="B227" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C227" t="s">
         <v>469</v>
@@ -8020,7 +8038,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>185</v>
+        <v>290</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -8028,7 +8046,7 @@
         <v>470</v>
       </c>
       <c r="B228" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C228" t="s">
         <v>471</v>
@@ -8040,7 +8058,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>172</v>
+        <v>255</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -8048,7 +8066,7 @@
         <v>472</v>
       </c>
       <c r="B229" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C229" t="s">
         <v>473</v>
@@ -8068,7 +8086,7 @@
         <v>474</v>
       </c>
       <c r="B230" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C230" t="s">
         <v>475</v>
@@ -8080,7 +8098,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>243</v>
+        <v>160</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -8088,7 +8106,7 @@
         <v>476</v>
       </c>
       <c r="B231" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C231" t="s">
         <v>477</v>
@@ -8100,7 +8118,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>115</v>
+        <v>282</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -8108,7 +8126,7 @@
         <v>478</v>
       </c>
       <c r="B232" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C232" t="s">
         <v>479</v>
@@ -8120,7 +8138,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>120</v>
+        <v>264</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -8128,7 +8146,7 @@
         <v>480</v>
       </c>
       <c r="B233" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C233" t="s">
         <v>481</v>
@@ -8140,7 +8158,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>164</v>
+        <v>101</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -8148,7 +8166,7 @@
         <v>482</v>
       </c>
       <c r="B234" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C234" t="s">
         <v>483</v>
@@ -8160,7 +8178,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>286</v>
+        <v>240</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -8168,7 +8186,7 @@
         <v>484</v>
       </c>
       <c r="B235" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C235" t="s">
         <v>485</v>
@@ -8180,7 +8198,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>283</v>
+        <v>132</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -8188,7 +8206,7 @@
         <v>486</v>
       </c>
       <c r="B236" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C236" t="s">
         <v>487</v>
@@ -8200,7 +8218,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>122</v>
+        <v>148</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -8220,7 +8238,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>139</v>
+        <v>117</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -8240,7 +8258,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -8260,7 +8278,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -8280,7 +8298,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -8300,7 +8318,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>287</v>
+        <v>112</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -8320,7 +8338,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>253</v>
+        <v>192</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -8340,7 +8358,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -8354,13 +8372,13 @@
         <v>504</v>
       </c>
       <c r="D244" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E244" t="s">
         <v>10</v>
       </c>
       <c r="F244">
-        <v>109</v>
+        <v>199</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -8380,7 +8398,7 @@
         <v>10</v>
       </c>
       <c r="F245">
-        <v>195</v>
+        <v>238</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -8400,7 +8418,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>160</v>
+        <v>102</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -8420,7 +8438,7 @@
         <v>10</v>
       </c>
       <c r="F247">
-        <v>172</v>
+        <v>208</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -8440,7 +8458,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>249</v>
+        <v>143</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -8460,7 +8478,7 @@
         <v>10</v>
       </c>
       <c r="F249">
-        <v>201</v>
+        <v>275</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -8480,7 +8498,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>193</v>
+        <v>130</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -8500,7 +8518,7 @@
         <v>10</v>
       </c>
       <c r="F251">
-        <v>117</v>
+        <v>148</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -8520,7 +8538,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>125</v>
+        <v>223</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -8540,7 +8558,7 @@
         <v>10</v>
       </c>
       <c r="F253">
-        <v>263</v>
+        <v>112</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -8560,7 +8578,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>294</v>
+        <v>267</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -8580,7 +8598,7 @@
         <v>10</v>
       </c>
       <c r="F255">
-        <v>116</v>
+        <v>299</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -8600,7 +8618,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>234</v>
+        <v>161</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -8620,7 +8638,7 @@
         <v>10</v>
       </c>
       <c r="F257">
-        <v>296</v>
+        <v>235</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -8640,7 +8658,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>258</v>
+        <v>152</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -8660,7 +8678,7 @@
         <v>10</v>
       </c>
       <c r="F259">
-        <v>202</v>
+        <v>170</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -8680,7 +8698,7 @@
         <v>10</v>
       </c>
       <c r="F260">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -8700,7 +8718,7 @@
         <v>10</v>
       </c>
       <c r="F261">
-        <v>274</v>
+        <v>125</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -8720,7 +8738,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -8740,7 +8758,7 @@
         <v>10</v>
       </c>
       <c r="F263">
-        <v>106</v>
+        <v>246</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -8754,13 +8772,13 @@
         <v>545</v>
       </c>
       <c r="D264" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E264" t="s">
         <v>10</v>
       </c>
       <c r="F264">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -8774,13 +8792,13 @@
         <v>547</v>
       </c>
       <c r="D265" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E265" t="s">
         <v>10</v>
       </c>
       <c r="F265">
-        <v>257</v>
+        <v>173</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -8794,13 +8812,13 @@
         <v>549</v>
       </c>
       <c r="D266" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E266" t="s">
         <v>10</v>
       </c>
       <c r="F266">
-        <v>205</v>
+        <v>129</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -8814,13 +8832,13 @@
         <v>551</v>
       </c>
       <c r="D267" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E267" t="s">
         <v>10</v>
       </c>
       <c r="F267">
-        <v>105</v>
+        <v>193</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -8834,13 +8852,13 @@
         <v>553</v>
       </c>
       <c r="D268" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E268" t="s">
         <v>10</v>
       </c>
       <c r="F268">
-        <v>157</v>
+        <v>296</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -8854,13 +8872,13 @@
         <v>555</v>
       </c>
       <c r="D269" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E269" t="s">
         <v>10</v>
       </c>
       <c r="F269">
-        <v>156</v>
+        <v>231</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -8874,13 +8892,13 @@
         <v>557</v>
       </c>
       <c r="D270" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E270" t="s">
         <v>10</v>
       </c>
       <c r="F270">
-        <v>115</v>
+        <v>196</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -8894,13 +8912,13 @@
         <v>559</v>
       </c>
       <c r="D271" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E271" t="s">
         <v>10</v>
       </c>
       <c r="F271">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -8914,13 +8932,13 @@
         <v>561</v>
       </c>
       <c r="D272" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E272" t="s">
         <v>10</v>
       </c>
       <c r="F272">
-        <v>158</v>
+        <v>262</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -8934,13 +8952,13 @@
         <v>563</v>
       </c>
       <c r="D273" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E273" t="s">
         <v>10</v>
       </c>
       <c r="F273">
-        <v>168</v>
+        <v>149</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -8948,39 +8966,39 @@
         <v>564</v>
       </c>
       <c r="B274" t="s">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="C274" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D274" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E274" t="s">
         <v>10</v>
       </c>
       <c r="F274">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B275" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C275" t="s">
         <v>568</v>
       </c>
       <c r="D275" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E275" t="s">
         <v>10</v>
       </c>
       <c r="F275">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -8988,19 +9006,19 @@
         <v>569</v>
       </c>
       <c r="B276" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C276" t="s">
         <v>570</v>
       </c>
       <c r="D276" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E276" t="s">
         <v>10</v>
       </c>
       <c r="F276">
-        <v>273</v>
+        <v>131</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -9008,19 +9026,19 @@
         <v>571</v>
       </c>
       <c r="B277" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C277" t="s">
         <v>572</v>
       </c>
       <c r="D277" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E277" t="s">
         <v>10</v>
       </c>
       <c r="F277">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -9028,19 +9046,19 @@
         <v>573</v>
       </c>
       <c r="B278" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C278" t="s">
         <v>574</v>
       </c>
       <c r="D278" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E278" t="s">
         <v>10</v>
       </c>
       <c r="F278">
-        <v>147</v>
+        <v>291</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -9048,19 +9066,19 @@
         <v>575</v>
       </c>
       <c r="B279" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C279" t="s">
         <v>576</v>
       </c>
       <c r="D279" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E279" t="s">
         <v>10</v>
       </c>
       <c r="F279">
-        <v>156</v>
+        <v>176</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -9068,19 +9086,19 @@
         <v>577</v>
       </c>
       <c r="B280" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C280" t="s">
         <v>578</v>
       </c>
       <c r="D280" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E280" t="s">
         <v>10</v>
       </c>
       <c r="F280">
-        <v>232</v>
+        <v>207</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -9088,19 +9106,19 @@
         <v>579</v>
       </c>
       <c r="B281" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C281" t="s">
         <v>580</v>
       </c>
       <c r="D281" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E281" t="s">
         <v>10</v>
       </c>
       <c r="F281">
-        <v>202</v>
+        <v>138</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -9108,19 +9126,19 @@
         <v>581</v>
       </c>
       <c r="B282" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C282" t="s">
         <v>582</v>
       </c>
       <c r="D282" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E282" t="s">
         <v>10</v>
       </c>
       <c r="F282">
-        <v>270</v>
+        <v>100</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -9128,19 +9146,19 @@
         <v>583</v>
       </c>
       <c r="B283" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C283" t="s">
         <v>584</v>
       </c>
       <c r="D283" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E283" t="s">
         <v>10</v>
       </c>
       <c r="F283">
-        <v>186</v>
+        <v>262</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -9148,19 +9166,19 @@
         <v>585</v>
       </c>
       <c r="B284" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C284" t="s">
         <v>586</v>
       </c>
       <c r="D284" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E284" t="s">
         <v>10</v>
       </c>
       <c r="F284">
-        <v>166</v>
+        <v>117</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -9168,19 +9186,19 @@
         <v>587</v>
       </c>
       <c r="B285" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C285" t="s">
         <v>588</v>
       </c>
       <c r="D285" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E285" t="s">
         <v>10</v>
       </c>
       <c r="F285">
-        <v>218</v>
+        <v>233</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -9188,19 +9206,19 @@
         <v>589</v>
       </c>
       <c r="B286" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C286" t="s">
         <v>590</v>
       </c>
       <c r="D286" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E286" t="s">
         <v>10</v>
       </c>
       <c r="F286">
-        <v>235</v>
+        <v>211</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -9208,19 +9226,19 @@
         <v>591</v>
       </c>
       <c r="B287" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C287" t="s">
         <v>592</v>
       </c>
       <c r="D287" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E287" t="s">
         <v>10</v>
       </c>
       <c r="F287">
-        <v>284</v>
+        <v>162</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -9228,19 +9246,19 @@
         <v>593</v>
       </c>
       <c r="B288" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C288" t="s">
         <v>594</v>
       </c>
       <c r="D288" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E288" t="s">
         <v>10</v>
       </c>
       <c r="F288">
-        <v>167</v>
+        <v>280</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -9248,19 +9266,19 @@
         <v>595</v>
       </c>
       <c r="B289" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C289" t="s">
         <v>596</v>
       </c>
       <c r="D289" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E289" t="s">
         <v>10</v>
       </c>
       <c r="F289">
-        <v>178</v>
+        <v>297</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -9268,19 +9286,19 @@
         <v>597</v>
       </c>
       <c r="B290" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C290" t="s">
         <v>598</v>
       </c>
       <c r="D290" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E290" t="s">
         <v>10</v>
       </c>
       <c r="F290">
-        <v>230</v>
+        <v>136</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -9288,19 +9306,19 @@
         <v>599</v>
       </c>
       <c r="B291" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C291" t="s">
         <v>600</v>
       </c>
       <c r="D291" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E291" t="s">
         <v>10</v>
       </c>
       <c r="F291">
-        <v>153</v>
+        <v>270</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -9308,19 +9326,19 @@
         <v>601</v>
       </c>
       <c r="B292" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C292" t="s">
         <v>602</v>
       </c>
       <c r="D292" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E292" t="s">
         <v>10</v>
       </c>
       <c r="F292">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -9328,19 +9346,19 @@
         <v>603</v>
       </c>
       <c r="B293" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C293" t="s">
         <v>604</v>
       </c>
       <c r="D293" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E293" t="s">
         <v>10</v>
       </c>
       <c r="F293">
-        <v>153</v>
+        <v>179</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -9348,19 +9366,19 @@
         <v>605</v>
       </c>
       <c r="B294" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C294" t="s">
         <v>606</v>
       </c>
       <c r="D294" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E294" t="s">
         <v>10</v>
       </c>
       <c r="F294">
-        <v>226</v>
+        <v>173</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -9368,19 +9386,19 @@
         <v>607</v>
       </c>
       <c r="B295" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C295" t="s">
         <v>608</v>
       </c>
       <c r="D295" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E295" t="s">
         <v>10</v>
       </c>
       <c r="F295">
-        <v>262</v>
+        <v>210</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -9388,19 +9406,19 @@
         <v>609</v>
       </c>
       <c r="B296" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C296" t="s">
         <v>610</v>
       </c>
       <c r="D296" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E296" t="s">
         <v>10</v>
       </c>
       <c r="F296">
-        <v>207</v>
+        <v>156</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -9408,19 +9426,19 @@
         <v>611</v>
       </c>
       <c r="B297" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C297" t="s">
         <v>612</v>
       </c>
       <c r="D297" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E297" t="s">
         <v>10</v>
       </c>
       <c r="F297">
-        <v>209</v>
+        <v>229</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -9428,19 +9446,19 @@
         <v>613</v>
       </c>
       <c r="B298" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C298" t="s">
         <v>614</v>
       </c>
       <c r="D298" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E298" t="s">
         <v>10</v>
       </c>
       <c r="F298">
-        <v>298</v>
+        <v>143</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -9448,19 +9466,19 @@
         <v>615</v>
       </c>
       <c r="B299" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C299" t="s">
         <v>616</v>
       </c>
       <c r="D299" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E299" t="s">
         <v>10</v>
       </c>
       <c r="F299">
-        <v>135</v>
+        <v>176</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -9468,19 +9486,19 @@
         <v>617</v>
       </c>
       <c r="B300" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C300" t="s">
         <v>618</v>
       </c>
       <c r="D300" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E300" t="s">
         <v>10</v>
       </c>
       <c r="F300">
-        <v>131</v>
+        <v>280</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -9488,19 +9506,19 @@
         <v>619</v>
       </c>
       <c r="B301" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C301" t="s">
         <v>620</v>
       </c>
       <c r="D301" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E301" t="s">
         <v>10</v>
       </c>
       <c r="F301">
-        <v>173</v>
+        <v>207</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -9508,19 +9526,19 @@
         <v>621</v>
       </c>
       <c r="B302" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C302" t="s">
         <v>622</v>
       </c>
       <c r="D302" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E302" t="s">
         <v>10</v>
       </c>
       <c r="F302">
-        <v>283</v>
+        <v>164</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -9528,19 +9546,19 @@
         <v>623</v>
       </c>
       <c r="B303" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C303" t="s">
         <v>624</v>
       </c>
       <c r="D303" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E303" t="s">
         <v>10</v>
       </c>
       <c r="F303">
-        <v>200</v>
+        <v>161</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -9548,19 +9566,19 @@
         <v>625</v>
       </c>
       <c r="B304" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C304" t="s">
         <v>626</v>
       </c>
       <c r="D304" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E304" t="s">
         <v>10</v>
       </c>
       <c r="F304">
-        <v>219</v>
+        <v>126</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -9568,19 +9586,19 @@
         <v>627</v>
       </c>
       <c r="B305" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C305" t="s">
         <v>628</v>
       </c>
       <c r="D305" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E305" t="s">
         <v>10</v>
       </c>
       <c r="F305">
-        <v>150</v>
+        <v>228</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -9588,19 +9606,19 @@
         <v>629</v>
       </c>
       <c r="B306" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C306" t="s">
         <v>630</v>
       </c>
       <c r="D306" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E306" t="s">
         <v>10</v>
       </c>
       <c r="F306">
-        <v>219</v>
+        <v>197</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -9608,19 +9626,19 @@
         <v>631</v>
       </c>
       <c r="B307" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C307" t="s">
         <v>632</v>
       </c>
       <c r="D307" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E307" t="s">
         <v>10</v>
       </c>
       <c r="F307">
-        <v>295</v>
+        <v>223</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -9628,19 +9646,19 @@
         <v>633</v>
       </c>
       <c r="B308" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C308" t="s">
         <v>634</v>
       </c>
       <c r="D308" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E308" t="s">
         <v>10</v>
       </c>
       <c r="F308">
-        <v>213</v>
+        <v>155</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -9648,19 +9666,19 @@
         <v>635</v>
       </c>
       <c r="B309" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C309" t="s">
         <v>636</v>
       </c>
       <c r="D309" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E309" t="s">
         <v>10</v>
       </c>
       <c r="F309">
-        <v>175</v>
+        <v>246</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -9668,19 +9686,19 @@
         <v>637</v>
       </c>
       <c r="B310" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C310" t="s">
         <v>638</v>
       </c>
       <c r="D310" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E310" t="s">
         <v>10</v>
       </c>
       <c r="F310">
-        <v>136</v>
+        <v>166</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -9688,19 +9706,19 @@
         <v>639</v>
       </c>
       <c r="B311" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C311" t="s">
         <v>640</v>
       </c>
       <c r="D311" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E311" t="s">
         <v>10</v>
       </c>
       <c r="F311">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -9708,19 +9726,19 @@
         <v>641</v>
       </c>
       <c r="B312" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C312" t="s">
         <v>642</v>
       </c>
       <c r="D312" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E312" t="s">
         <v>10</v>
       </c>
       <c r="F312">
-        <v>253</v>
+        <v>135</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -9728,7 +9746,7 @@
         <v>643</v>
       </c>
       <c r="B313" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C313" t="s">
         <v>644</v>
@@ -9740,7 +9758,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>296</v>
+        <v>160</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -9760,7 +9778,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>124</v>
+        <v>193</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -9780,7 +9798,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>290</v>
+        <v>268</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -9800,7 +9818,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>260</v>
+        <v>180</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -9820,7 +9838,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>299</v>
+        <v>216</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -9840,7 +9858,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>218</v>
+        <v>242</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -9860,7 +9878,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>250</v>
+        <v>229</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -9880,7 +9898,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -9900,7 +9918,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>283</v>
+        <v>200</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -9920,7 +9938,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>216</v>
+        <v>136</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -9940,7 +9958,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>155</v>
+        <v>259</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -9960,7 +9978,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -9980,7 +9998,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>297</v>
+        <v>225</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -10000,7 +10018,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -10020,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>154</v>
+        <v>264</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -10040,7 +10058,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>160</v>
+        <v>126</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -10060,7 +10078,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -10080,7 +10098,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>252</v>
+        <v>183</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -10100,7 +10118,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>198</v>
+        <v>146</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -10120,7 +10138,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>294</v>
+        <v>139</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -10140,7 +10158,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>287</v>
+        <v>242</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -10160,7 +10178,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>233</v>
+        <v>299</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -10180,7 +10198,7 @@
         <v>10</v>
       </c>
       <c r="F335">
-        <v>203</v>
+        <v>258</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -10200,7 +10218,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>106</v>
+        <v>125</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -10220,7 +10238,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>210</v>
+        <v>142</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -10240,7 +10258,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>238</v>
+        <v>283</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -10260,7 +10278,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -10280,7 +10298,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>148</v>
+        <v>113</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -10300,7 +10318,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -10320,7 +10338,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>127</v>
+        <v>185</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -10340,7 +10358,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>245</v>
+        <v>264</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -10360,7 +10378,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>296</v>
+        <v>105</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -10380,7 +10398,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>107</v>
+        <v>213</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -10400,7 +10418,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>275</v>
+        <v>132</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -10420,7 +10438,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>133</v>
+        <v>270</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -10440,7 +10458,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>189</v>
+        <v>120</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -10460,7 +10478,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>244</v>
+        <v>261</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -10480,7 +10498,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -10500,7 +10518,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -10520,7 +10538,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>153</v>
+        <v>188</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -10540,7 +10558,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -10560,7 +10578,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -10580,7 +10598,7 @@
         <v>10</v>
       </c>
       <c r="F355">
-        <v>233</v>
+        <v>166</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -10600,7 +10618,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>153</v>
+        <v>190</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -10620,7 +10638,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>131</v>
+        <v>156</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -10640,7 +10658,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>139</v>
+        <v>102</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -10660,7 +10678,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>117</v>
+        <v>296</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -10680,7 +10698,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>217</v>
+        <v>202</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -10700,7 +10718,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>215</v>
+        <v>233</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -10720,7 +10738,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>234</v>
+        <v>108</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -10740,7 +10758,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>206</v>
+        <v>162</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -10760,7 +10778,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>205</v>
+        <v>219</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -10780,7 +10798,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>118</v>
+        <v>160</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -10800,7 +10818,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -10820,7 +10838,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>135</v>
+        <v>211</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -10840,7 +10858,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>217</v>
+        <v>179</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -10860,7 +10878,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -10880,7 +10898,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>141</v>
+        <v>291</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -10900,7 +10918,7 @@
         <v>10</v>
       </c>
       <c r="F371">
-        <v>137</v>
+        <v>244</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -10920,7 +10938,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>249</v>
+        <v>141</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -10940,7 +10958,7 @@
         <v>10</v>
       </c>
       <c r="F373">
-        <v>150</v>
+        <v>176</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -10960,7 +10978,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>113</v>
+        <v>232</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -10980,7 +10998,7 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>186</v>
+        <v>217</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -11000,7 +11018,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -11020,7 +11038,7 @@
         <v>10</v>
       </c>
       <c r="F377">
-        <v>164</v>
+        <v>145</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -11040,7 +11058,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>265</v>
+        <v>176</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -11060,7 +11078,7 @@
         <v>10</v>
       </c>
       <c r="F379">
-        <v>285</v>
+        <v>190</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -11080,7 +11098,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>110</v>
+        <v>243</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -11100,7 +11118,7 @@
         <v>10</v>
       </c>
       <c r="F381">
-        <v>187</v>
+        <v>112</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -11120,7 +11138,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>244</v>
+        <v>299</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -11140,7 +11158,7 @@
         <v>10</v>
       </c>
       <c r="F383">
-        <v>294</v>
+        <v>177</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -11160,7 +11178,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>294</v>
+        <v>115</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -11180,7 +11198,7 @@
         <v>10</v>
       </c>
       <c r="F385">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -11200,7 +11218,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>295</v>
+        <v>222</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -11220,7 +11238,7 @@
         <v>10</v>
       </c>
       <c r="F387">
-        <v>127</v>
+        <v>195</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -11240,7 +11258,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>113</v>
+        <v>164</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -11260,7 +11278,7 @@
         <v>10</v>
       </c>
       <c r="F389">
-        <v>249</v>
+        <v>296</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -11280,7 +11298,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>213</v>
+        <v>190</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -11300,7 +11318,7 @@
         <v>10</v>
       </c>
       <c r="F391">
-        <v>286</v>
+        <v>125</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -11320,7 +11338,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>175</v>
+        <v>213</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -11340,7 +11358,7 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>117</v>
+        <v>262</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -11360,7 +11378,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>205</v>
+        <v>160</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -11380,7 +11398,7 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>118</v>
+        <v>236</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -11400,7 +11418,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>171</v>
+        <v>255</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -11420,7 +11438,7 @@
         <v>10</v>
       </c>
       <c r="F397">
-        <v>163</v>
+        <v>107</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -11440,7 +11458,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>224</v>
+        <v>121</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -11460,7 +11478,7 @@
         <v>10</v>
       </c>
       <c r="F399">
-        <v>182</v>
+        <v>137</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -11480,7 +11498,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>235</v>
+        <v>185</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -11500,7 +11518,7 @@
         <v>10</v>
       </c>
       <c r="F401">
-        <v>202</v>
+        <v>227</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -11520,7 +11538,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>285</v>
+        <v>127</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -11540,7 +11558,7 @@
         <v>10</v>
       </c>
       <c r="F403">
-        <v>172</v>
+        <v>147</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -11560,7 +11578,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -11580,7 +11598,7 @@
         <v>10</v>
       </c>
       <c r="F405">
-        <v>246</v>
+        <v>195</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -11600,7 +11618,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -11620,7 +11638,7 @@
         <v>10</v>
       </c>
       <c r="F407">
-        <v>225</v>
+        <v>150</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -11640,7 +11658,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>271</v>
+        <v>222</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -11660,7 +11678,7 @@
         <v>10</v>
       </c>
       <c r="F409">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -11680,7 +11698,7 @@
         <v>10</v>
       </c>
       <c r="F410">
-        <v>106</v>
+        <v>291</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -11700,7 +11718,7 @@
         <v>10</v>
       </c>
       <c r="F411">
-        <v>273</v>
+        <v>202</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -11720,7 +11738,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>195</v>
+        <v>168</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -11734,13 +11752,13 @@
         <v>850</v>
       </c>
       <c r="D413" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E413" t="s">
         <v>10</v>
       </c>
       <c r="F413">
-        <v>216</v>
+        <v>246</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -11754,13 +11772,13 @@
         <v>852</v>
       </c>
       <c r="D414" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E414" t="s">
         <v>10</v>
       </c>
       <c r="F414">
-        <v>267</v>
+        <v>134</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -11774,13 +11792,13 @@
         <v>854</v>
       </c>
       <c r="D415" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E415" t="s">
         <v>10</v>
       </c>
       <c r="F415">
-        <v>243</v>
+        <v>112</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -11794,13 +11812,13 @@
         <v>856</v>
       </c>
       <c r="D416" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E416" t="s">
         <v>10</v>
       </c>
       <c r="F416">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -11820,7 +11838,7 @@
         <v>10</v>
       </c>
       <c r="F417">
-        <v>283</v>
+        <v>257</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -11840,7 +11858,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>246</v>
+        <v>263</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -11860,7 +11878,7 @@
         <v>10</v>
       </c>
       <c r="F419">
-        <v>132</v>
+        <v>289</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -11880,7 +11898,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>192</v>
+        <v>139</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -11900,7 +11918,7 @@
         <v>10</v>
       </c>
       <c r="F421">
-        <v>156</v>
+        <v>265</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -11920,7 +11938,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>213</v>
+        <v>117</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -11934,13 +11952,13 @@
         <v>871</v>
       </c>
       <c r="D423" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E423" t="s">
         <v>10</v>
       </c>
       <c r="F423">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -11954,13 +11972,13 @@
         <v>873</v>
       </c>
       <c r="D424" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E424" t="s">
         <v>10</v>
       </c>
       <c r="F424">
-        <v>287</v>
+        <v>132</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -11974,13 +11992,13 @@
         <v>875</v>
       </c>
       <c r="D425" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E425" t="s">
         <v>10</v>
       </c>
       <c r="F425">
-        <v>284</v>
+        <v>231</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -11994,13 +12012,13 @@
         <v>877</v>
       </c>
       <c r="D426" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E426" t="s">
         <v>10</v>
       </c>
       <c r="F426">
-        <v>299</v>
+        <v>140</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -12014,13 +12032,13 @@
         <v>879</v>
       </c>
       <c r="D427" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E427" t="s">
         <v>10</v>
       </c>
       <c r="F427">
-        <v>286</v>
+        <v>247</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -12034,13 +12052,13 @@
         <v>881</v>
       </c>
       <c r="D428" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E428" t="s">
         <v>10</v>
       </c>
       <c r="F428">
-        <v>227</v>
+        <v>177</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -12054,13 +12072,13 @@
         <v>883</v>
       </c>
       <c r="D429" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E429" t="s">
         <v>10</v>
       </c>
       <c r="F429">
-        <v>206</v>
+        <v>120</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -12074,13 +12092,13 @@
         <v>885</v>
       </c>
       <c r="D430" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E430" t="s">
         <v>10</v>
       </c>
       <c r="F430">
-        <v>138</v>
+        <v>237</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -12094,13 +12112,13 @@
         <v>887</v>
       </c>
       <c r="D431" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E431" t="s">
         <v>10</v>
       </c>
       <c r="F431">
-        <v>280</v>
+        <v>195</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -12108,10 +12126,10 @@
         <v>888</v>
       </c>
       <c r="B432" t="s">
-        <v>870</v>
+        <v>889</v>
       </c>
       <c r="C432" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D432" t="s">
         <v>9</v>
@@ -12120,27 +12138,27 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>132</v>
+        <v>222</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B433" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C433" t="s">
         <v>892</v>
       </c>
       <c r="D433" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E433" t="s">
         <v>10</v>
       </c>
       <c r="F433">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -12148,19 +12166,19 @@
         <v>893</v>
       </c>
       <c r="B434" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C434" t="s">
         <v>894</v>
       </c>
       <c r="D434" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E434" t="s">
         <v>10</v>
       </c>
       <c r="F434">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -12168,19 +12186,19 @@
         <v>895</v>
       </c>
       <c r="B435" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C435" t="s">
         <v>896</v>
       </c>
       <c r="D435" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E435" t="s">
         <v>10</v>
       </c>
       <c r="F435">
-        <v>289</v>
+        <v>195</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -12188,19 +12206,19 @@
         <v>897</v>
       </c>
       <c r="B436" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C436" t="s">
         <v>898</v>
       </c>
       <c r="D436" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E436" t="s">
         <v>10</v>
       </c>
       <c r="F436">
-        <v>131</v>
+        <v>209</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -12208,19 +12226,19 @@
         <v>899</v>
       </c>
       <c r="B437" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C437" t="s">
         <v>900</v>
       </c>
       <c r="D437" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E437" t="s">
         <v>10</v>
       </c>
       <c r="F437">
-        <v>223</v>
+        <v>278</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -12228,19 +12246,19 @@
         <v>901</v>
       </c>
       <c r="B438" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C438" t="s">
         <v>902</v>
       </c>
       <c r="D438" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E438" t="s">
         <v>10</v>
       </c>
       <c r="F438">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -12248,19 +12266,19 @@
         <v>903</v>
       </c>
       <c r="B439" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C439" t="s">
         <v>904</v>
       </c>
       <c r="D439" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E439" t="s">
         <v>10</v>
       </c>
       <c r="F439">
-        <v>264</v>
+        <v>193</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -12268,19 +12286,19 @@
         <v>905</v>
       </c>
       <c r="B440" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C440" t="s">
         <v>906</v>
       </c>
       <c r="D440" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E440" t="s">
         <v>10</v>
       </c>
       <c r="F440">
-        <v>125</v>
+        <v>168</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -12288,19 +12306,19 @@
         <v>907</v>
       </c>
       <c r="B441" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C441" t="s">
         <v>908</v>
       </c>
       <c r="D441" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E441" t="s">
         <v>10</v>
       </c>
       <c r="F441">
-        <v>118</v>
+        <v>196</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -12308,19 +12326,19 @@
         <v>909</v>
       </c>
       <c r="B442" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C442" t="s">
         <v>910</v>
       </c>
       <c r="D442" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E442" t="s">
         <v>10</v>
       </c>
       <c r="F442">
-        <v>128</v>
+        <v>198</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -12328,19 +12346,19 @@
         <v>911</v>
       </c>
       <c r="B443" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C443" t="s">
         <v>912</v>
       </c>
       <c r="D443" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E443" t="s">
         <v>10</v>
       </c>
       <c r="F443">
-        <v>213</v>
+        <v>103</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -12348,19 +12366,19 @@
         <v>913</v>
       </c>
       <c r="B444" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C444" t="s">
         <v>914</v>
       </c>
       <c r="D444" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E444" t="s">
         <v>10</v>
       </c>
       <c r="F444">
-        <v>142</v>
+        <v>166</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -12368,19 +12386,19 @@
         <v>915</v>
       </c>
       <c r="B445" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C445" t="s">
         <v>916</v>
       </c>
       <c r="D445" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E445" t="s">
         <v>10</v>
       </c>
       <c r="F445">
-        <v>179</v>
+        <v>252</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -12388,19 +12406,19 @@
         <v>917</v>
       </c>
       <c r="B446" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C446" t="s">
         <v>918</v>
       </c>
       <c r="D446" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E446" t="s">
         <v>10</v>
       </c>
       <c r="F446">
-        <v>251</v>
+        <v>149</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -12408,19 +12426,19 @@
         <v>919</v>
       </c>
       <c r="B447" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C447" t="s">
         <v>920</v>
       </c>
       <c r="D447" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E447" t="s">
         <v>10</v>
       </c>
       <c r="F447">
-        <v>113</v>
+        <v>201</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -12428,7 +12446,7 @@
         <v>921</v>
       </c>
       <c r="B448" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C448" t="s">
         <v>922</v>
@@ -12440,7 +12458,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>251</v>
+        <v>174</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -12448,7 +12466,7 @@
         <v>923</v>
       </c>
       <c r="B449" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C449" t="s">
         <v>924</v>
@@ -12460,7 +12478,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>207</v>
+        <v>174</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -12468,7 +12486,7 @@
         <v>925</v>
       </c>
       <c r="B450" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C450" t="s">
         <v>926</v>
@@ -12480,7 +12498,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>299</v>
+        <v>271</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -12488,7 +12506,7 @@
         <v>927</v>
       </c>
       <c r="B451" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C451" t="s">
         <v>928</v>
@@ -12500,7 +12518,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -12520,7 +12538,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>121</v>
+        <v>156</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -12540,7 +12558,7 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>244</v>
+        <v>223</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -12560,7 +12578,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>146</v>
+        <v>107</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -12580,7 +12598,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>252</v>
+        <v>124</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -12600,7 +12618,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>293</v>
+        <v>169</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -12620,7 +12638,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>243</v>
+        <v>284</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -12640,7 +12658,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>270</v>
+        <v>176</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -12660,7 +12678,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -12680,7 +12698,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>268</v>
+        <v>242</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -12700,7 +12718,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>256</v>
+        <v>192</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -12720,7 +12738,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -12740,7 +12758,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -12760,7 +12778,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>224</v>
+        <v>174</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -12780,7 +12798,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>115</v>
+        <v>299</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -12800,7 +12818,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>138</v>
+        <v>265</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -12820,7 +12838,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -12840,7 +12858,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>198</v>
+        <v>127</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -12854,13 +12872,13 @@
         <v>965</v>
       </c>
       <c r="D469" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E469" t="s">
         <v>10</v>
       </c>
       <c r="F469">
-        <v>136</v>
+        <v>106</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -12874,13 +12892,13 @@
         <v>967</v>
       </c>
       <c r="D470" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E470" t="s">
         <v>10</v>
       </c>
       <c r="F470">
-        <v>268</v>
+        <v>248</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -12894,13 +12912,13 @@
         <v>969</v>
       </c>
       <c r="D471" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E471" t="s">
         <v>10</v>
       </c>
       <c r="F471">
-        <v>279</v>
+        <v>258</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -12914,13 +12932,13 @@
         <v>971</v>
       </c>
       <c r="D472" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E472" t="s">
         <v>10</v>
       </c>
       <c r="F472">
-        <v>153</v>
+        <v>176</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -12934,13 +12952,13 @@
         <v>973</v>
       </c>
       <c r="D473" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E473" t="s">
         <v>10</v>
       </c>
       <c r="F473">
-        <v>275</v>
+        <v>161</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -12954,13 +12972,13 @@
         <v>975</v>
       </c>
       <c r="D474" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E474" t="s">
         <v>10</v>
       </c>
       <c r="F474">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -12974,13 +12992,13 @@
         <v>977</v>
       </c>
       <c r="D475" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E475" t="s">
         <v>10</v>
       </c>
       <c r="F475">
-        <v>204</v>
+        <v>282</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -12994,13 +13012,13 @@
         <v>979</v>
       </c>
       <c r="D476" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E476" t="s">
         <v>10</v>
       </c>
       <c r="F476">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -13014,13 +13032,13 @@
         <v>981</v>
       </c>
       <c r="D477" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E477" t="s">
         <v>10</v>
       </c>
       <c r="F477">
-        <v>159</v>
+        <v>261</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -13034,13 +13052,13 @@
         <v>983</v>
       </c>
       <c r="D478" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E478" t="s">
         <v>10</v>
       </c>
       <c r="F478">
-        <v>258</v>
+        <v>182</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -13054,7 +13072,7 @@
         <v>985</v>
       </c>
       <c r="D479" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E479" t="s">
         <v>10</v>
@@ -13074,13 +13092,13 @@
         <v>987</v>
       </c>
       <c r="D480" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E480" t="s">
         <v>10</v>
       </c>
       <c r="F480">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -13094,13 +13112,13 @@
         <v>989</v>
       </c>
       <c r="D481" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E481" t="s">
         <v>10</v>
       </c>
       <c r="F481">
-        <v>260</v>
+        <v>189</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -13114,13 +13132,13 @@
         <v>991</v>
       </c>
       <c r="D482" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E482" t="s">
         <v>10</v>
       </c>
       <c r="F482">
-        <v>104</v>
+        <v>248</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -13134,13 +13152,13 @@
         <v>993</v>
       </c>
       <c r="D483" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E483" t="s">
         <v>10</v>
       </c>
       <c r="F483">
-        <v>235</v>
+        <v>183</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -13154,13 +13172,13 @@
         <v>995</v>
       </c>
       <c r="D484" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E484" t="s">
         <v>10</v>
       </c>
       <c r="F484">
-        <v>182</v>
+        <v>255</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -13174,13 +13192,13 @@
         <v>997</v>
       </c>
       <c r="D485" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E485" t="s">
         <v>10</v>
       </c>
       <c r="F485">
-        <v>192</v>
+        <v>295</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -13194,13 +13212,13 @@
         <v>999</v>
       </c>
       <c r="D486" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E486" t="s">
         <v>10</v>
       </c>
       <c r="F486">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -13214,13 +13232,13 @@
         <v>1001</v>
       </c>
       <c r="D487" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E487" t="s">
         <v>10</v>
       </c>
       <c r="F487">
-        <v>298</v>
+        <v>246</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -13234,13 +13252,13 @@
         <v>1003</v>
       </c>
       <c r="D488" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E488" t="s">
         <v>10</v>
       </c>
       <c r="F488">
-        <v>109</v>
+        <v>298</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -13254,13 +13272,13 @@
         <v>1005</v>
       </c>
       <c r="D489" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E489" t="s">
         <v>10</v>
       </c>
       <c r="F489">
-        <v>288</v>
+        <v>171</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -13274,13 +13292,13 @@
         <v>1007</v>
       </c>
       <c r="D490" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E490" t="s">
         <v>10</v>
       </c>
       <c r="F490">
-        <v>286</v>
+        <v>228</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -13294,13 +13312,13 @@
         <v>1009</v>
       </c>
       <c r="D491" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E491" t="s">
         <v>10</v>
       </c>
       <c r="F491">
-        <v>103</v>
+        <v>258</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -13314,13 +13332,13 @@
         <v>1011</v>
       </c>
       <c r="D492" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E492" t="s">
         <v>10</v>
       </c>
       <c r="F492">
-        <v>292</v>
+        <v>279</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -13334,13 +13352,13 @@
         <v>1013</v>
       </c>
       <c r="D493" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E493" t="s">
         <v>10</v>
       </c>
       <c r="F493">
-        <v>243</v>
+        <v>178</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -13354,13 +13372,13 @@
         <v>1015</v>
       </c>
       <c r="D494" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E494" t="s">
         <v>10</v>
       </c>
       <c r="F494">
-        <v>287</v>
+        <v>177</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -13374,13 +13392,13 @@
         <v>1017</v>
       </c>
       <c r="D495" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E495" t="s">
         <v>10</v>
       </c>
       <c r="F495">
-        <v>254</v>
+        <v>117</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -13394,13 +13412,13 @@
         <v>1019</v>
       </c>
       <c r="D496" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E496" t="s">
         <v>10</v>
       </c>
       <c r="F496">
-        <v>121</v>
+        <v>236</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -13420,7 +13438,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>265</v>
+        <v>166</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -13440,7 +13458,67 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>155</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B499" t="s">
+        <v>930</v>
+      </c>
+      <c r="C499" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D499" t="s">
+        <v>16</v>
+      </c>
+      <c r="E499" t="s">
+        <v>10</v>
+      </c>
+      <c r="F499">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B500" t="s">
+        <v>930</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D500" t="s">
+        <v>9</v>
+      </c>
+      <c r="E500" t="s">
+        <v>10</v>
+      </c>
+      <c r="F500">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B501" t="s">
+        <v>930</v>
+      </c>
+      <c r="C501" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D501" t="s">
+        <v>13</v>
+      </c>
+      <c r="E501" t="s">
+        <v>10</v>
+      </c>
+      <c r="F501">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
